--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154328</v>
+        <v>122152404</v>
       </c>
       <c r="B20" t="n">
-        <v>79726</v>
+        <v>90779</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479349</v>
+        <v>479269</v>
       </c>
       <c r="R20" t="n">
-        <v>6951738</v>
+        <v>6951404</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2943,22 +2943,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154282</v>
+        <v>122152379</v>
       </c>
       <c r="B21" t="n">
-        <v>57527</v>
+        <v>90779</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2971,34 +2971,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478995</v>
+        <v>479244</v>
       </c>
       <c r="R21" t="n">
-        <v>6951732</v>
+        <v>6951379</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,22 +3045,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152404</v>
+        <v>122154286</v>
       </c>
       <c r="B22" t="n">
-        <v>90779</v>
+        <v>95722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,34 +3073,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479269</v>
+        <v>479067</v>
       </c>
       <c r="R22" t="n">
-        <v>6951404</v>
+        <v>6951710</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3147,22 +3147,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154287</v>
+        <v>122154283</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>79761</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3171,20 +3171,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3192,21 +3192,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479072</v>
+        <v>479028</v>
       </c>
       <c r="R23" t="n">
-        <v>6951714</v>
+        <v>6951741</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3265,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152377</v>
+        <v>122152386</v>
       </c>
       <c r="B24" t="n">
-        <v>91065</v>
+        <v>90797</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,34 +3277,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479251</v>
+        <v>479347</v>
       </c>
       <c r="R24" t="n">
-        <v>6951369</v>
+        <v>6951521</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,10 +3363,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152403</v>
+        <v>122152382</v>
       </c>
       <c r="B25" t="n">
-        <v>91065</v>
+        <v>74738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3379,25 +3375,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3407,10 +3403,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479265</v>
+        <v>479342</v>
       </c>
       <c r="R25" t="n">
-        <v>6951415</v>
+        <v>6951436</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3469,10 +3465,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152400</v>
+        <v>122154338</v>
       </c>
       <c r="B26" t="n">
-        <v>74739</v>
+        <v>79726</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3485,21 +3481,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3509,10 +3505,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479288</v>
+        <v>479524</v>
       </c>
       <c r="R26" t="n">
-        <v>6951411</v>
+        <v>6951553</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3539,12 +3535,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,22 +3555,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152409</v>
+        <v>122152401</v>
       </c>
       <c r="B27" t="n">
-        <v>90797</v>
+        <v>91065</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3587,34 +3583,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479277</v>
+        <v>479280</v>
       </c>
       <c r="R27" t="n">
-        <v>6951379</v>
+        <v>6951418</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3673,10 +3669,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154331</v>
+        <v>122152388</v>
       </c>
       <c r="B28" t="n">
-        <v>79726</v>
+        <v>91065</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3689,21 +3685,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3713,10 +3709,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479485</v>
+        <v>479294</v>
       </c>
       <c r="R28" t="n">
-        <v>6951601</v>
+        <v>6951503</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,12 +3739,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,22 +3759,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152407</v>
+        <v>122154284</v>
       </c>
       <c r="B29" t="n">
-        <v>90779</v>
+        <v>79726</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3791,34 +3787,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479274</v>
+        <v>479048</v>
       </c>
       <c r="R29" t="n">
-        <v>6951393</v>
+        <v>6951711</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3845,17 +3841,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,22 +3861,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152388</v>
+        <v>122152400</v>
       </c>
       <c r="B30" t="n">
-        <v>91065</v>
+        <v>74739</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3898,21 +3889,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3922,10 +3913,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479294</v>
+        <v>479288</v>
       </c>
       <c r="R30" t="n">
-        <v>6951503</v>
+        <v>6951411</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3984,7 +3975,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152395</v>
+        <v>122152377</v>
       </c>
       <c r="B31" t="n">
         <v>91065</v>
@@ -4020,14 +4011,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479310</v>
+        <v>479251</v>
       </c>
       <c r="R31" t="n">
-        <v>6951439</v>
+        <v>6951369</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4086,10 +4077,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154338</v>
+        <v>122152395</v>
       </c>
       <c r="B32" t="n">
-        <v>79726</v>
+        <v>91065</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4102,21 +4093,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4126,10 +4117,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479524</v>
+        <v>479310</v>
       </c>
       <c r="R32" t="n">
-        <v>6951553</v>
+        <v>6951439</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4156,12 +4147,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,22 +4167,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152386</v>
+        <v>122152380</v>
       </c>
       <c r="B33" t="n">
-        <v>90797</v>
+        <v>88097</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4204,34 +4195,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479347</v>
+        <v>479313</v>
       </c>
       <c r="R33" t="n">
-        <v>6951521</v>
+        <v>6951347</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4290,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152379</v>
+        <v>122154280</v>
       </c>
       <c r="B34" t="n">
-        <v>90779</v>
+        <v>79630</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4302,38 +4293,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479244</v>
+        <v>479029</v>
       </c>
       <c r="R34" t="n">
-        <v>6951379</v>
+        <v>6951739</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4360,12 +4351,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,22 +4371,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154285</v>
+        <v>122152383</v>
       </c>
       <c r="B35" t="n">
-        <v>57485</v>
+        <v>91435</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4404,42 +4395,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>898</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479073</v>
+        <v>479355</v>
       </c>
       <c r="R35" t="n">
-        <v>6951703</v>
+        <v>6951440</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4466,12 +4453,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4486,22 +4478,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152385</v>
+        <v>122154331</v>
       </c>
       <c r="B36" t="n">
-        <v>91712</v>
+        <v>79726</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4510,25 +4502,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4538,10 +4530,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479374</v>
+        <v>479485</v>
       </c>
       <c r="R36" t="n">
-        <v>6951500</v>
+        <v>6951601</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4568,12 +4560,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,22 +4580,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154284</v>
+        <v>122152409</v>
       </c>
       <c r="B37" t="n">
-        <v>79726</v>
+        <v>90797</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4616,34 +4608,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479048</v>
+        <v>479277</v>
       </c>
       <c r="R37" t="n">
-        <v>6951711</v>
+        <v>6951379</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4670,12 +4662,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,22 +4682,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152392</v>
+        <v>122152385</v>
       </c>
       <c r="B38" t="n">
-        <v>91219</v>
+        <v>91712</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4714,25 +4706,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4742,10 +4734,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479310</v>
+        <v>479374</v>
       </c>
       <c r="R38" t="n">
-        <v>6951454</v>
+        <v>6951500</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4804,10 +4796,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152383</v>
+        <v>122152376</v>
       </c>
       <c r="B39" t="n">
-        <v>91435</v>
+        <v>97129</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4816,38 +4808,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>898</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479355</v>
+        <v>479264</v>
       </c>
       <c r="R39" t="n">
-        <v>6951440</v>
+        <v>6951354</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4884,7 +4880,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
+          <t>Riklig förekomst i skogen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4893,6 +4889,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4911,7 +4908,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152401</v>
+        <v>122152403</v>
       </c>
       <c r="B40" t="n">
         <v>91065</v>
@@ -4951,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479280</v>
+        <v>479265</v>
       </c>
       <c r="R40" t="n">
-        <v>6951418</v>
+        <v>6951415</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5013,10 +5010,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154280</v>
+        <v>122154328</v>
       </c>
       <c r="B41" t="n">
-        <v>79630</v>
+        <v>79726</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5025,38 +5022,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479029</v>
+        <v>479349</v>
       </c>
       <c r="R41" t="n">
-        <v>6951739</v>
+        <v>6951738</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5083,12 +5080,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5115,10 +5112,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152410</v>
+        <v>122152392</v>
       </c>
       <c r="B42" t="n">
-        <v>97129</v>
+        <v>91219</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5127,42 +5124,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479306</v>
+        <v>479310</v>
       </c>
       <c r="R42" t="n">
-        <v>6951356</v>
+        <v>6951454</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5203,7 +5196,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5222,10 +5214,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122152376</v>
+        <v>122154287</v>
       </c>
       <c r="B43" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5234,42 +5226,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479264</v>
+        <v>479072</v>
       </c>
       <c r="R43" t="n">
-        <v>6951354</v>
+        <v>6951714</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5296,17 +5288,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogen.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5315,29 +5302,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122152382</v>
+        <v>122152410</v>
       </c>
       <c r="B44" t="n">
-        <v>74738</v>
+        <v>97129</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5346,38 +5332,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>492</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479342</v>
+        <v>479306</v>
       </c>
       <c r="R44" t="n">
-        <v>6951436</v>
+        <v>6951356</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5418,6 +5408,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5436,10 +5427,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122152380</v>
+        <v>122154282</v>
       </c>
       <c r="B45" t="n">
-        <v>88097</v>
+        <v>57527</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5452,34 +5443,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479313</v>
+        <v>478995</v>
       </c>
       <c r="R45" t="n">
-        <v>6951347</v>
+        <v>6951732</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5506,12 +5497,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5526,22 +5517,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154286</v>
+        <v>122154285</v>
       </c>
       <c r="B46" t="n">
-        <v>95722</v>
+        <v>57485</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5550,38 +5541,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479067</v>
+        <v>479073</v>
       </c>
       <c r="R46" t="n">
-        <v>6951710</v>
+        <v>6951703</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5640,10 +5635,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122152397</v>
+        <v>122152407</v>
       </c>
       <c r="B47" t="n">
-        <v>90797</v>
+        <v>90779</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5656,21 +5651,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5680,10 +5675,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479310</v>
+        <v>479274</v>
       </c>
       <c r="R47" t="n">
-        <v>6951433</v>
+        <v>6951393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5716,6 +5711,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5742,10 +5742,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154283</v>
+        <v>122152397</v>
       </c>
       <c r="B48" t="n">
-        <v>79761</v>
+        <v>90797</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5754,38 +5754,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479028</v>
+        <v>479310</v>
       </c>
       <c r="R48" t="n">
-        <v>6951741</v>
+        <v>6951433</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,12 +5832,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -3261,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152386</v>
+        <v>122152382</v>
       </c>
       <c r="B24" t="n">
-        <v>90797</v>
+        <v>74738</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3273,25 +3273,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479347</v>
+        <v>479342</v>
       </c>
       <c r="R24" t="n">
-        <v>6951521</v>
+        <v>6951436</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152382</v>
+        <v>122152386</v>
       </c>
       <c r="B25" t="n">
-        <v>74738</v>
+        <v>90797</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3375,25 +3375,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479342</v>
+        <v>479347</v>
       </c>
       <c r="R25" t="n">
-        <v>6951436</v>
+        <v>6951521</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152401</v>
+        <v>122154284</v>
       </c>
       <c r="B27" t="n">
-        <v>91065</v>
+        <v>79726</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3583,34 +3583,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479280</v>
+        <v>479048</v>
       </c>
       <c r="R27" t="n">
-        <v>6951418</v>
+        <v>6951711</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3657,19 +3657,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152388</v>
+        <v>122152401</v>
       </c>
       <c r="B28" t="n">
         <v>91065</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479294</v>
+        <v>479280</v>
       </c>
       <c r="R28" t="n">
-        <v>6951503</v>
+        <v>6951418</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154284</v>
+        <v>122152388</v>
       </c>
       <c r="B29" t="n">
-        <v>79726</v>
+        <v>91065</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3787,34 +3787,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479048</v>
+        <v>479294</v>
       </c>
       <c r="R29" t="n">
-        <v>6951711</v>
+        <v>6951503</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3861,12 +3861,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122152410</v>
+        <v>122154282</v>
       </c>
       <c r="B44" t="n">
-        <v>97129</v>
+        <v>57527</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5332,42 +5332,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479306</v>
+        <v>478995</v>
       </c>
       <c r="R44" t="n">
-        <v>6951356</v>
+        <v>6951732</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5394,12 +5390,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5408,29 +5404,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154282</v>
+        <v>122152410</v>
       </c>
       <c r="B45" t="n">
-        <v>57527</v>
+        <v>97129</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5439,38 +5434,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478995</v>
+        <v>479306</v>
       </c>
       <c r="R45" t="n">
-        <v>6951732</v>
+        <v>6951356</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5497,12 +5496,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5511,18 +5510,19 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122152407</v>
+        <v>122152397</v>
       </c>
       <c r="B47" t="n">
-        <v>90779</v>
+        <v>90797</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479274</v>
+        <v>479310</v>
       </c>
       <c r="R47" t="n">
-        <v>6951393</v>
+        <v>6951433</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5711,11 +5711,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5742,10 +5737,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122152397</v>
+        <v>122152407</v>
       </c>
       <c r="B48" t="n">
-        <v>90797</v>
+        <v>90779</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5758,21 +5753,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479310</v>
+        <v>479274</v>
       </c>
       <c r="R48" t="n">
-        <v>6951433</v>
+        <v>6951393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5818,6 +5813,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152404</v>
+        <v>122154286</v>
       </c>
       <c r="B20" t="n">
-        <v>90779</v>
+        <v>95732</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2869,34 +2869,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479269</v>
+        <v>479067</v>
       </c>
       <c r="R20" t="n">
-        <v>6951404</v>
+        <v>6951710</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2943,22 +2943,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152379</v>
+        <v>122152382</v>
       </c>
       <c r="B21" t="n">
-        <v>90779</v>
+        <v>74738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2967,38 +2967,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479244</v>
+        <v>479342</v>
       </c>
       <c r="R21" t="n">
-        <v>6951379</v>
+        <v>6951436</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154286</v>
+        <v>122152401</v>
       </c>
       <c r="B22" t="n">
-        <v>95722</v>
+        <v>91075</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,34 +3073,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479067</v>
+        <v>479280</v>
       </c>
       <c r="R22" t="n">
-        <v>6951710</v>
+        <v>6951418</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3147,22 +3147,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154283</v>
+        <v>122154328</v>
       </c>
       <c r="B23" t="n">
-        <v>79761</v>
+        <v>79727</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3171,38 +3171,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479028</v>
+        <v>479349</v>
       </c>
       <c r="R23" t="n">
-        <v>6951741</v>
+        <v>6951738</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3261,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152382</v>
+        <v>122152392</v>
       </c>
       <c r="B24" t="n">
-        <v>74738</v>
+        <v>91229</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>492</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479342</v>
+        <v>479310</v>
       </c>
       <c r="R24" t="n">
-        <v>6951436</v>
+        <v>6951454</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152386</v>
+        <v>122152407</v>
       </c>
       <c r="B25" t="n">
-        <v>90797</v>
+        <v>90789</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479347</v>
+        <v>479274</v>
       </c>
       <c r="R25" t="n">
-        <v>6951521</v>
+        <v>6951393</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3439,6 +3439,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3465,10 +3470,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154338</v>
+        <v>122152379</v>
       </c>
       <c r="B26" t="n">
-        <v>79726</v>
+        <v>90789</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,34 +3486,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479524</v>
+        <v>479244</v>
       </c>
       <c r="R26" t="n">
-        <v>6951553</v>
+        <v>6951379</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3535,12 +3540,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3555,22 +3560,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154284</v>
+        <v>122152388</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>91075</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3583,34 +3588,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479048</v>
+        <v>479294</v>
       </c>
       <c r="R27" t="n">
-        <v>6951711</v>
+        <v>6951503</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,12 +3642,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3657,22 +3662,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152401</v>
+        <v>122154285</v>
       </c>
       <c r="B28" t="n">
-        <v>91065</v>
+        <v>57485</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,38 +3686,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479280</v>
+        <v>479073</v>
       </c>
       <c r="R28" t="n">
-        <v>6951418</v>
+        <v>6951703</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3739,12 +3748,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3759,22 +3768,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152388</v>
+        <v>122152386</v>
       </c>
       <c r="B29" t="n">
-        <v>91065</v>
+        <v>90807</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3787,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3811,10 +3820,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479294</v>
+        <v>479347</v>
       </c>
       <c r="R29" t="n">
-        <v>6951503</v>
+        <v>6951521</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3873,10 +3882,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152400</v>
+        <v>122154280</v>
       </c>
       <c r="B30" t="n">
-        <v>74739</v>
+        <v>79631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3885,38 +3894,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479288</v>
+        <v>479029</v>
       </c>
       <c r="R30" t="n">
-        <v>6951411</v>
+        <v>6951739</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3943,12 +3952,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3963,22 +3972,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152377</v>
+        <v>122154331</v>
       </c>
       <c r="B31" t="n">
-        <v>91065</v>
+        <v>79727</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3991,34 +4000,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479251</v>
+        <v>479485</v>
       </c>
       <c r="R31" t="n">
-        <v>6951369</v>
+        <v>6951601</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4045,12 +4054,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,22 +4074,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152395</v>
+        <v>122152385</v>
       </c>
       <c r="B32" t="n">
-        <v>91065</v>
+        <v>91722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4089,25 +4098,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4117,10 +4126,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479310</v>
+        <v>479374</v>
       </c>
       <c r="R32" t="n">
-        <v>6951439</v>
+        <v>6951500</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4179,10 +4188,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152380</v>
+        <v>122152403</v>
       </c>
       <c r="B33" t="n">
-        <v>88097</v>
+        <v>91075</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,34 +4204,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479313</v>
+        <v>479265</v>
       </c>
       <c r="R33" t="n">
-        <v>6951347</v>
+        <v>6951415</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4281,10 +4290,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154280</v>
+        <v>122154283</v>
       </c>
       <c r="B34" t="n">
-        <v>79630</v>
+        <v>79762</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4297,21 +4306,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479029</v>
+        <v>479028</v>
       </c>
       <c r="R34" t="n">
-        <v>6951739</v>
+        <v>6951741</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4386,7 +4395,7 @@
         <v>122152383</v>
       </c>
       <c r="B35" t="n">
-        <v>91435</v>
+        <v>91445</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4490,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154331</v>
+        <v>122152380</v>
       </c>
       <c r="B36" t="n">
-        <v>79726</v>
+        <v>88107</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,34 +4515,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479485</v>
+        <v>479313</v>
       </c>
       <c r="R36" t="n">
-        <v>6951601</v>
+        <v>6951347</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4560,12 +4569,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4580,22 +4589,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152409</v>
+        <v>122152410</v>
       </c>
       <c r="B37" t="n">
-        <v>90797</v>
+        <v>97139</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4604,38 +4613,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479277</v>
+        <v>479306</v>
       </c>
       <c r="R37" t="n">
-        <v>6951379</v>
+        <v>6951356</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4676,6 +4689,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4694,10 +4708,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152385</v>
+        <v>122154338</v>
       </c>
       <c r="B38" t="n">
-        <v>91712</v>
+        <v>79727</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4706,25 +4720,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4734,10 +4748,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479374</v>
+        <v>479524</v>
       </c>
       <c r="R38" t="n">
-        <v>6951500</v>
+        <v>6951553</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4764,12 +4778,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4784,22 +4798,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152376</v>
+        <v>122152397</v>
       </c>
       <c r="B39" t="n">
-        <v>97129</v>
+        <v>90807</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4808,42 +4822,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479264</v>
+        <v>479310</v>
       </c>
       <c r="R39" t="n">
-        <v>6951354</v>
+        <v>6951433</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4878,18 +4888,12 @@
           <t>2024-08-29</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogen.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4908,10 +4912,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152403</v>
+        <v>122152404</v>
       </c>
       <c r="B40" t="n">
-        <v>91065</v>
+        <v>90789</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4924,21 +4928,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4948,10 +4952,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479265</v>
+        <v>479269</v>
       </c>
       <c r="R40" t="n">
-        <v>6951415</v>
+        <v>6951404</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,10 +5014,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154328</v>
+        <v>122154282</v>
       </c>
       <c r="B41" t="n">
-        <v>79726</v>
+        <v>57527</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5026,34 +5030,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479349</v>
+        <v>478995</v>
       </c>
       <c r="R41" t="n">
-        <v>6951738</v>
+        <v>6951732</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5080,12 +5084,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5112,10 +5116,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152392</v>
+        <v>122152409</v>
       </c>
       <c r="B42" t="n">
-        <v>91219</v>
+        <v>90807</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5124,38 +5128,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479310</v>
+        <v>479277</v>
       </c>
       <c r="R42" t="n">
-        <v>6951454</v>
+        <v>6951379</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5214,10 +5218,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154287</v>
+        <v>122152395</v>
       </c>
       <c r="B43" t="n">
-        <v>78645</v>
+        <v>91075</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5230,38 +5234,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479072</v>
+        <v>479310</v>
       </c>
       <c r="R43" t="n">
-        <v>6951714</v>
+        <v>6951439</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5308,22 +5308,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154282</v>
+        <v>122154284</v>
       </c>
       <c r="B44" t="n">
-        <v>57527</v>
+        <v>79727</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5336,21 +5336,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478995</v>
+        <v>479048</v>
       </c>
       <c r="R44" t="n">
-        <v>6951732</v>
+        <v>6951711</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5422,10 +5422,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122152410</v>
+        <v>122154287</v>
       </c>
       <c r="B45" t="n">
-        <v>97129</v>
+        <v>78646</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5434,42 +5434,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479306</v>
+        <v>479072</v>
       </c>
       <c r="R45" t="n">
-        <v>6951356</v>
+        <v>6951714</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5510,29 +5510,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154285</v>
+        <v>122152400</v>
       </c>
       <c r="B46" t="n">
-        <v>57485</v>
+        <v>74739</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5541,42 +5540,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479073</v>
+        <v>479288</v>
       </c>
       <c r="R46" t="n">
-        <v>6951703</v>
+        <v>6951411</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5603,12 +5598,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5623,22 +5618,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122152397</v>
+        <v>122152377</v>
       </c>
       <c r="B47" t="n">
-        <v>90797</v>
+        <v>91075</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5651,34 +5646,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479310</v>
+        <v>479251</v>
       </c>
       <c r="R47" t="n">
-        <v>6951433</v>
+        <v>6951369</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5737,10 +5732,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122152407</v>
+        <v>122152376</v>
       </c>
       <c r="B48" t="n">
-        <v>90779</v>
+        <v>97139</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5749,38 +5744,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479274</v>
+        <v>479264</v>
       </c>
       <c r="R48" t="n">
-        <v>6951393</v>
+        <v>6951354</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5817,7 +5816,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+          <t>Riklig förekomst i skogen.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5826,6 +5825,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154286</v>
+        <v>122152401</v>
       </c>
       <c r="B20" t="n">
-        <v>95732</v>
+        <v>91075</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2869,34 +2869,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479067</v>
+        <v>479280</v>
       </c>
       <c r="R20" t="n">
-        <v>6951710</v>
+        <v>6951418</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2943,22 +2943,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152382</v>
+        <v>122152385</v>
       </c>
       <c r="B21" t="n">
-        <v>74738</v>
+        <v>91722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2967,25 +2967,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479342</v>
+        <v>479374</v>
       </c>
       <c r="R21" t="n">
-        <v>6951436</v>
+        <v>6951500</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152401</v>
+        <v>122152400</v>
       </c>
       <c r="B22" t="n">
-        <v>91075</v>
+        <v>74739</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,21 +3073,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479280</v>
+        <v>479288</v>
       </c>
       <c r="R22" t="n">
-        <v>6951418</v>
+        <v>6951411</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3159,7 +3159,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154328</v>
+        <v>122154331</v>
       </c>
       <c r="B23" t="n">
         <v>79727</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479349</v>
+        <v>479485</v>
       </c>
       <c r="R23" t="n">
-        <v>6951738</v>
+        <v>6951601</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152392</v>
+        <v>122152388</v>
       </c>
       <c r="B24" t="n">
-        <v>91229</v>
+        <v>91075</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3273,25 +3273,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479310</v>
+        <v>479294</v>
       </c>
       <c r="R24" t="n">
-        <v>6951454</v>
+        <v>6951503</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152407</v>
+        <v>122154328</v>
       </c>
       <c r="B25" t="n">
-        <v>90789</v>
+        <v>79727</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479274</v>
+        <v>479349</v>
       </c>
       <c r="R25" t="n">
-        <v>6951393</v>
+        <v>6951738</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3433,17 +3433,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3458,12 +3453,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3572,10 +3567,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152388</v>
+        <v>122152376</v>
       </c>
       <c r="B27" t="n">
-        <v>91075</v>
+        <v>97139</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3584,38 +3579,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479294</v>
+        <v>479264</v>
       </c>
       <c r="R27" t="n">
-        <v>6951503</v>
+        <v>6951354</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3650,12 +3649,18 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogen.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3674,10 +3679,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154285</v>
+        <v>122152377</v>
       </c>
       <c r="B28" t="n">
-        <v>57485</v>
+        <v>91075</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3686,42 +3691,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479073</v>
+        <v>479251</v>
       </c>
       <c r="R28" t="n">
-        <v>6951703</v>
+        <v>6951369</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3748,12 +3749,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,22 +3769,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152386</v>
+        <v>122154280</v>
       </c>
       <c r="B29" t="n">
-        <v>90807</v>
+        <v>79631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3792,38 +3793,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479347</v>
+        <v>479029</v>
       </c>
       <c r="R29" t="n">
-        <v>6951521</v>
+        <v>6951739</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3850,12 +3851,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,22 +3871,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154280</v>
+        <v>122152386</v>
       </c>
       <c r="B30" t="n">
-        <v>79631</v>
+        <v>90807</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,38 +3895,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479029</v>
+        <v>479347</v>
       </c>
       <c r="R30" t="n">
-        <v>6951739</v>
+        <v>6951521</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3952,12 +3953,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3972,22 +3973,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154331</v>
+        <v>122152397</v>
       </c>
       <c r="B31" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4000,21 +4001,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4024,10 +4025,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479485</v>
+        <v>479310</v>
       </c>
       <c r="R31" t="n">
-        <v>6951601</v>
+        <v>6951433</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4054,12 +4055,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4074,22 +4075,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152385</v>
+        <v>122152404</v>
       </c>
       <c r="B32" t="n">
-        <v>91722</v>
+        <v>90789</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4098,25 +4099,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4126,10 +4127,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479374</v>
+        <v>479269</v>
       </c>
       <c r="R32" t="n">
-        <v>6951500</v>
+        <v>6951404</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4188,7 +4189,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152403</v>
+        <v>122152395</v>
       </c>
       <c r="B33" t="n">
         <v>91075</v>
@@ -4228,10 +4229,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479265</v>
+        <v>479310</v>
       </c>
       <c r="R33" t="n">
-        <v>6951415</v>
+        <v>6951439</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4392,10 +4393,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152383</v>
+        <v>122152392</v>
       </c>
       <c r="B35" t="n">
-        <v>91445</v>
+        <v>91229</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4408,21 +4409,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4432,10 +4433,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479355</v>
+        <v>479310</v>
       </c>
       <c r="R35" t="n">
-        <v>6951440</v>
+        <v>6951454</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4468,11 +4469,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4499,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152380</v>
+        <v>122152407</v>
       </c>
       <c r="B36" t="n">
-        <v>88107</v>
+        <v>90789</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4515,34 +4511,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479313</v>
+        <v>479274</v>
       </c>
       <c r="R36" t="n">
-        <v>6951347</v>
+        <v>6951393</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4575,6 +4571,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4601,10 +4602,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122152410</v>
+        <v>122154282</v>
       </c>
       <c r="B37" t="n">
-        <v>97139</v>
+        <v>57527</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4613,42 +4614,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479306</v>
+        <v>478995</v>
       </c>
       <c r="R37" t="n">
-        <v>6951356</v>
+        <v>6951732</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4675,12 +4672,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4689,19 +4686,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4810,10 +4806,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152397</v>
+        <v>122152382</v>
       </c>
       <c r="B39" t="n">
-        <v>90807</v>
+        <v>74738</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4822,25 +4818,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4850,10 +4846,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479310</v>
+        <v>479342</v>
       </c>
       <c r="R39" t="n">
-        <v>6951433</v>
+        <v>6951436</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4912,10 +4908,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152404</v>
+        <v>122152410</v>
       </c>
       <c r="B40" t="n">
-        <v>90789</v>
+        <v>97139</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4924,38 +4920,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479269</v>
+        <v>479306</v>
       </c>
       <c r="R40" t="n">
-        <v>6951404</v>
+        <v>6951356</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4996,6 +4996,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5014,10 +5015,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154282</v>
+        <v>122152409</v>
       </c>
       <c r="B41" t="n">
-        <v>57527</v>
+        <v>90807</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5030,34 +5031,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478995</v>
+        <v>479277</v>
       </c>
       <c r="R41" t="n">
-        <v>6951732</v>
+        <v>6951379</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5084,12 +5085,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5104,22 +5105,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152409</v>
+        <v>122152403</v>
       </c>
       <c r="B42" t="n">
-        <v>90807</v>
+        <v>91075</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5132,34 +5133,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479277</v>
+        <v>479265</v>
       </c>
       <c r="R42" t="n">
-        <v>6951379</v>
+        <v>6951415</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5218,10 +5219,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122152395</v>
+        <v>122154287</v>
       </c>
       <c r="B43" t="n">
-        <v>91075</v>
+        <v>78646</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5234,34 +5235,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479310</v>
+        <v>479072</v>
       </c>
       <c r="R43" t="n">
-        <v>6951439</v>
+        <v>6951714</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5288,12 +5293,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5308,22 +5313,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154284</v>
+        <v>122152383</v>
       </c>
       <c r="B44" t="n">
-        <v>79727</v>
+        <v>91445</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5332,38 +5337,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479048</v>
+        <v>479355</v>
       </c>
       <c r="R44" t="n">
-        <v>6951711</v>
+        <v>6951440</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5390,12 +5395,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5410,22 +5420,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154287</v>
+        <v>122152380</v>
       </c>
       <c r="B45" t="n">
-        <v>78646</v>
+        <v>88107</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5438,38 +5448,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479072</v>
+        <v>479313</v>
       </c>
       <c r="R45" t="n">
-        <v>6951714</v>
+        <v>6951347</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5496,12 +5502,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5516,22 +5522,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122152400</v>
+        <v>122154286</v>
       </c>
       <c r="B46" t="n">
-        <v>74739</v>
+        <v>95732</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5544,34 +5550,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479288</v>
+        <v>479067</v>
       </c>
       <c r="R46" t="n">
-        <v>6951411</v>
+        <v>6951710</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5598,12 +5604,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5618,22 +5624,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122152377</v>
+        <v>122154284</v>
       </c>
       <c r="B47" t="n">
-        <v>91075</v>
+        <v>79727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5646,34 +5652,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479251</v>
+        <v>479048</v>
       </c>
       <c r="R47" t="n">
-        <v>6951369</v>
+        <v>6951711</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5700,12 +5706,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5720,22 +5726,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122152376</v>
+        <v>122154285</v>
       </c>
       <c r="B48" t="n">
-        <v>97139</v>
+        <v>57485</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5748,38 +5754,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479264</v>
+        <v>479073</v>
       </c>
       <c r="R48" t="n">
-        <v>6951354</v>
+        <v>6951703</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5806,17 +5812,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogen.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5825,19 +5826,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154331</v>
+        <v>122152388</v>
       </c>
       <c r="B23" t="n">
-        <v>79727</v>
+        <v>91075</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3175,21 +3175,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479485</v>
+        <v>479294</v>
       </c>
       <c r="R23" t="n">
-        <v>6951601</v>
+        <v>6951503</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3249,22 +3249,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152388</v>
+        <v>122154331</v>
       </c>
       <c r="B24" t="n">
-        <v>91075</v>
+        <v>79727</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479294</v>
+        <v>479485</v>
       </c>
       <c r="R24" t="n">
-        <v>6951503</v>
+        <v>6951601</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3331,12 +3331,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3351,12 +3351,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152409</v>
+        <v>122152403</v>
       </c>
       <c r="B41" t="n">
-        <v>90807</v>
+        <v>91075</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479277</v>
+        <v>479265</v>
       </c>
       <c r="R41" t="n">
-        <v>6951379</v>
+        <v>6951415</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5117,10 +5117,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152403</v>
+        <v>122152409</v>
       </c>
       <c r="B42" t="n">
-        <v>91075</v>
+        <v>90807</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5133,34 +5133,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479265</v>
+        <v>479277</v>
       </c>
       <c r="R42" t="n">
-        <v>6951415</v>
+        <v>6951379</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122152380</v>
+        <v>122154284</v>
       </c>
       <c r="B45" t="n">
-        <v>88107</v>
+        <v>79727</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5448,34 +5448,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479313</v>
+        <v>479048</v>
       </c>
       <c r="R45" t="n">
-        <v>6951347</v>
+        <v>6951711</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5502,12 +5502,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5522,22 +5522,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154286</v>
+        <v>122154285</v>
       </c>
       <c r="B46" t="n">
-        <v>95732</v>
+        <v>57485</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5546,38 +5546,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479067</v>
+        <v>479073</v>
       </c>
       <c r="R46" t="n">
-        <v>6951710</v>
+        <v>6951703</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5636,10 +5640,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154284</v>
+        <v>122154286</v>
       </c>
       <c r="B47" t="n">
-        <v>79727</v>
+        <v>95732</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5652,21 +5656,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5676,10 +5680,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479048</v>
+        <v>479067</v>
       </c>
       <c r="R47" t="n">
-        <v>6951711</v>
+        <v>6951710</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5738,10 +5742,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154285</v>
+        <v>122152380</v>
       </c>
       <c r="B48" t="n">
-        <v>57485</v>
+        <v>88107</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5750,42 +5754,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479073</v>
+        <v>479313</v>
       </c>
       <c r="R48" t="n">
-        <v>6951703</v>
+        <v>6951347</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,12 +5832,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152401</v>
+        <v>122154287</v>
       </c>
       <c r="B20" t="n">
-        <v>91075</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2869,34 +2869,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479280</v>
+        <v>479072</v>
       </c>
       <c r="R20" t="n">
-        <v>6951418</v>
+        <v>6951714</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2923,12 +2927,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2943,22 +2947,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152385</v>
+        <v>122154331</v>
       </c>
       <c r="B21" t="n">
-        <v>91722</v>
+        <v>79732</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2967,25 +2971,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2995,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479374</v>
+        <v>479485</v>
       </c>
       <c r="R21" t="n">
-        <v>6951500</v>
+        <v>6951601</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3025,12 +3029,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,22 +3049,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152400</v>
+        <v>122152380</v>
       </c>
       <c r="B22" t="n">
-        <v>74739</v>
+        <v>88119</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,34 +3077,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479288</v>
+        <v>479313</v>
       </c>
       <c r="R22" t="n">
-        <v>6951411</v>
+        <v>6951347</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3159,10 +3163,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152388</v>
+        <v>122154280</v>
       </c>
       <c r="B23" t="n">
-        <v>91075</v>
+        <v>79636</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3171,38 +3175,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479294</v>
+        <v>479029</v>
       </c>
       <c r="R23" t="n">
-        <v>6951503</v>
+        <v>6951739</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3229,12 +3233,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3249,22 +3253,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154331</v>
+        <v>122152386</v>
       </c>
       <c r="B24" t="n">
-        <v>79727</v>
+        <v>90819</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,21 +3281,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,10 +3305,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479485</v>
+        <v>479347</v>
       </c>
       <c r="R24" t="n">
-        <v>6951601</v>
+        <v>6951521</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3331,12 +3335,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3351,22 +3355,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154328</v>
+        <v>122152403</v>
       </c>
       <c r="B25" t="n">
-        <v>79727</v>
+        <v>91087</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3379,21 +3383,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3403,10 +3407,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479349</v>
+        <v>479265</v>
       </c>
       <c r="R25" t="n">
-        <v>6951738</v>
+        <v>6951415</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3433,12 +3437,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3453,22 +3457,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152379</v>
+        <v>122152401</v>
       </c>
       <c r="B26" t="n">
-        <v>90789</v>
+        <v>91087</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,34 +3485,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479244</v>
+        <v>479280</v>
       </c>
       <c r="R26" t="n">
-        <v>6951379</v>
+        <v>6951418</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3570,7 +3574,7 @@
         <v>122152376</v>
       </c>
       <c r="B27" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3679,10 +3683,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152377</v>
+        <v>122152410</v>
       </c>
       <c r="B28" t="n">
-        <v>91075</v>
+        <v>97151</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3691,38 +3695,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479251</v>
+        <v>479306</v>
       </c>
       <c r="R28" t="n">
-        <v>6951369</v>
+        <v>6951356</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3763,6 +3771,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3781,10 +3790,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154280</v>
+        <v>122154284</v>
       </c>
       <c r="B29" t="n">
-        <v>79631</v>
+        <v>79732</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3793,25 +3802,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3821,10 +3830,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479029</v>
+        <v>479048</v>
       </c>
       <c r="R29" t="n">
-        <v>6951739</v>
+        <v>6951711</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3883,10 +3892,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152386</v>
+        <v>122154338</v>
       </c>
       <c r="B30" t="n">
-        <v>90807</v>
+        <v>79732</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3899,21 +3908,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3923,10 +3932,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479347</v>
+        <v>479524</v>
       </c>
       <c r="R30" t="n">
-        <v>6951521</v>
+        <v>6951553</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3953,12 +3962,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3973,22 +3982,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152397</v>
+        <v>122152385</v>
       </c>
       <c r="B31" t="n">
-        <v>90807</v>
+        <v>91734</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3997,25 +4006,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4025,10 +4034,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479310</v>
+        <v>479374</v>
       </c>
       <c r="R31" t="n">
-        <v>6951433</v>
+        <v>6951500</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4087,10 +4096,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152404</v>
+        <v>122152388</v>
       </c>
       <c r="B32" t="n">
-        <v>90789</v>
+        <v>91087</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4103,21 +4112,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4127,10 +4136,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479269</v>
+        <v>479294</v>
       </c>
       <c r="R32" t="n">
-        <v>6951404</v>
+        <v>6951503</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4189,10 +4198,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152395</v>
+        <v>122154285</v>
       </c>
       <c r="B33" t="n">
-        <v>91075</v>
+        <v>57490</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4201,38 +4210,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479310</v>
+        <v>479073</v>
       </c>
       <c r="R33" t="n">
-        <v>6951439</v>
+        <v>6951703</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4259,12 +4272,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,22 +4292,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154283</v>
+        <v>122152397</v>
       </c>
       <c r="B34" t="n">
-        <v>79762</v>
+        <v>90819</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4303,38 +4316,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479028</v>
+        <v>479310</v>
       </c>
       <c r="R34" t="n">
-        <v>6951741</v>
+        <v>6951433</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4361,12 +4374,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,22 +4394,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152392</v>
+        <v>122154283</v>
       </c>
       <c r="B35" t="n">
-        <v>91229</v>
+        <v>79767</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4405,38 +4418,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479310</v>
+        <v>479028</v>
       </c>
       <c r="R35" t="n">
-        <v>6951454</v>
+        <v>6951741</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4463,12 +4476,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,12 +4496,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4498,7 +4511,7 @@
         <v>122152407</v>
       </c>
       <c r="B36" t="n">
-        <v>90789</v>
+        <v>90801</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4602,10 +4615,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154282</v>
+        <v>122154286</v>
       </c>
       <c r="B37" t="n">
-        <v>57527</v>
+        <v>95744</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4618,21 +4631,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4642,10 +4655,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478995</v>
+        <v>479067</v>
       </c>
       <c r="R37" t="n">
-        <v>6951732</v>
+        <v>6951710</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4704,10 +4717,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154338</v>
+        <v>122152404</v>
       </c>
       <c r="B38" t="n">
-        <v>79727</v>
+        <v>90801</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4720,21 +4733,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4744,10 +4757,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479524</v>
+        <v>479269</v>
       </c>
       <c r="R38" t="n">
-        <v>6951553</v>
+        <v>6951404</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4774,12 +4787,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,22 +4807,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152382</v>
+        <v>122152379</v>
       </c>
       <c r="B39" t="n">
-        <v>74738</v>
+        <v>90801</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4818,38 +4831,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479342</v>
+        <v>479244</v>
       </c>
       <c r="R39" t="n">
-        <v>6951436</v>
+        <v>6951379</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4908,10 +4921,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152410</v>
+        <v>122154282</v>
       </c>
       <c r="B40" t="n">
-        <v>97139</v>
+        <v>57532</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4920,42 +4933,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479306</v>
+        <v>478995</v>
       </c>
       <c r="R40" t="n">
-        <v>6951356</v>
+        <v>6951732</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4982,12 +4991,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4996,29 +5005,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152403</v>
+        <v>122152377</v>
       </c>
       <c r="B41" t="n">
-        <v>91075</v>
+        <v>91087</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5051,14 +5059,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479265</v>
+        <v>479251</v>
       </c>
       <c r="R41" t="n">
-        <v>6951415</v>
+        <v>6951369</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5117,10 +5125,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152409</v>
+        <v>122152382</v>
       </c>
       <c r="B42" t="n">
-        <v>90807</v>
+        <v>74743</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5129,38 +5137,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479277</v>
+        <v>479342</v>
       </c>
       <c r="R42" t="n">
-        <v>6951379</v>
+        <v>6951436</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5219,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154287</v>
+        <v>122154328</v>
       </c>
       <c r="B43" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5235,38 +5243,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479072</v>
+        <v>479349</v>
       </c>
       <c r="R43" t="n">
-        <v>6951714</v>
+        <v>6951738</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5293,12 +5297,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5328,7 +5332,7 @@
         <v>122152383</v>
       </c>
       <c r="B44" t="n">
-        <v>91445</v>
+        <v>91457</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5432,10 +5436,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154284</v>
+        <v>122152392</v>
       </c>
       <c r="B45" t="n">
-        <v>79727</v>
+        <v>91241</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5444,38 +5448,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479048</v>
+        <v>479310</v>
       </c>
       <c r="R45" t="n">
-        <v>6951711</v>
+        <v>6951454</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5502,12 +5506,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5522,22 +5526,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154285</v>
+        <v>122152395</v>
       </c>
       <c r="B46" t="n">
-        <v>57485</v>
+        <v>91087</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5546,42 +5550,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479073</v>
+        <v>479310</v>
       </c>
       <c r="R46" t="n">
-        <v>6951703</v>
+        <v>6951439</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5628,22 +5628,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154286</v>
+        <v>122152409</v>
       </c>
       <c r="B47" t="n">
-        <v>95732</v>
+        <v>90819</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5656,34 +5656,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479067</v>
+        <v>479277</v>
       </c>
       <c r="R47" t="n">
-        <v>6951710</v>
+        <v>6951379</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5710,12 +5710,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5730,22 +5730,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122152380</v>
+        <v>122152400</v>
       </c>
       <c r="B48" t="n">
-        <v>88107</v>
+        <v>74744</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5758,34 +5758,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479313</v>
+        <v>479288</v>
       </c>
       <c r="R48" t="n">
-        <v>6951347</v>
+        <v>6951411</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154287</v>
+        <v>122152404</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>90808</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2869,38 +2869,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479072</v>
+        <v>479269</v>
       </c>
       <c r="R20" t="n">
-        <v>6951714</v>
+        <v>6951404</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2927,12 +2923,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2947,22 +2943,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154331</v>
+        <v>122152400</v>
       </c>
       <c r="B21" t="n">
-        <v>79732</v>
+        <v>74744</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2975,21 +2971,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2999,10 +2995,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479485</v>
+        <v>479288</v>
       </c>
       <c r="R21" t="n">
-        <v>6951601</v>
+        <v>6951411</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3029,12 +3025,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,22 +3045,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152380</v>
+        <v>122152401</v>
       </c>
       <c r="B22" t="n">
-        <v>88119</v>
+        <v>91092</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3077,34 +3073,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479313</v>
+        <v>479280</v>
       </c>
       <c r="R22" t="n">
-        <v>6951347</v>
+        <v>6951418</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3163,10 +3159,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154280</v>
+        <v>122152386</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>90826</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3175,38 +3171,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479029</v>
+        <v>479347</v>
       </c>
       <c r="R23" t="n">
-        <v>6951739</v>
+        <v>6951521</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3233,12 +3229,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3253,22 +3249,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152386</v>
+        <v>122152380</v>
       </c>
       <c r="B24" t="n">
-        <v>90819</v>
+        <v>88123</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,34 +3277,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479347</v>
+        <v>479313</v>
       </c>
       <c r="R24" t="n">
-        <v>6951521</v>
+        <v>6951347</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,10 +3363,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152403</v>
+        <v>122152377</v>
       </c>
       <c r="B25" t="n">
-        <v>91087</v>
+        <v>91092</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3403,14 +3399,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479265</v>
+        <v>479251</v>
       </c>
       <c r="R25" t="n">
-        <v>6951415</v>
+        <v>6951369</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3469,10 +3465,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152401</v>
+        <v>122154286</v>
       </c>
       <c r="B26" t="n">
-        <v>91087</v>
+        <v>95749</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3485,34 +3481,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479280</v>
+        <v>479067</v>
       </c>
       <c r="R26" t="n">
-        <v>6951418</v>
+        <v>6951710</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3539,12 +3535,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,22 +3555,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152376</v>
+        <v>122154328</v>
       </c>
       <c r="B27" t="n">
-        <v>97151</v>
+        <v>79732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3583,42 +3579,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479264</v>
+        <v>479349</v>
       </c>
       <c r="R27" t="n">
-        <v>6951354</v>
+        <v>6951738</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3645,17 +3637,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogen.</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3664,29 +3651,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152410</v>
+        <v>122152397</v>
       </c>
       <c r="B28" t="n">
-        <v>97151</v>
+        <v>90826</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,42 +3681,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479306</v>
+        <v>479310</v>
       </c>
       <c r="R28" t="n">
-        <v>6951356</v>
+        <v>6951433</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3771,7 +3753,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3790,10 +3771,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154284</v>
+        <v>122152383</v>
       </c>
       <c r="B29" t="n">
-        <v>79732</v>
+        <v>91462</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3802,38 +3783,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479048</v>
+        <v>479355</v>
       </c>
       <c r="R29" t="n">
-        <v>6951711</v>
+        <v>6951440</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3860,12 +3841,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,22 +3866,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154338</v>
+        <v>122152388</v>
       </c>
       <c r="B30" t="n">
-        <v>79732</v>
+        <v>91092</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3908,21 +3894,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3932,10 +3918,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479524</v>
+        <v>479294</v>
       </c>
       <c r="R30" t="n">
-        <v>6951553</v>
+        <v>6951503</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3962,12 +3948,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,22 +3968,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152385</v>
+        <v>122152395</v>
       </c>
       <c r="B31" t="n">
-        <v>91734</v>
+        <v>91092</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4006,25 +3992,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4034,10 +4020,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479374</v>
+        <v>479310</v>
       </c>
       <c r="R31" t="n">
-        <v>6951500</v>
+        <v>6951439</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4096,10 +4082,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152388</v>
+        <v>122152376</v>
       </c>
       <c r="B32" t="n">
-        <v>91087</v>
+        <v>97156</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4108,38 +4094,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479294</v>
+        <v>479264</v>
       </c>
       <c r="R32" t="n">
-        <v>6951503</v>
+        <v>6951354</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4174,12 +4164,18 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogen.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4198,10 +4194,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154285</v>
+        <v>122154284</v>
       </c>
       <c r="B33" t="n">
-        <v>57490</v>
+        <v>79732</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4210,42 +4206,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479073</v>
+        <v>479048</v>
       </c>
       <c r="R33" t="n">
-        <v>6951703</v>
+        <v>6951711</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4304,10 +4296,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152397</v>
+        <v>122154280</v>
       </c>
       <c r="B34" t="n">
-        <v>90819</v>
+        <v>79636</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4316,38 +4308,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479310</v>
+        <v>479029</v>
       </c>
       <c r="R34" t="n">
-        <v>6951433</v>
+        <v>6951739</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4374,12 +4366,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4394,22 +4386,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154283</v>
+        <v>122152410</v>
       </c>
       <c r="B35" t="n">
-        <v>79767</v>
+        <v>97156</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4422,34 +4414,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479028</v>
+        <v>479306</v>
       </c>
       <c r="R35" t="n">
-        <v>6951741</v>
+        <v>6951356</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4476,12 +4472,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,28 +4486,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152407</v>
+        <v>122152385</v>
       </c>
       <c r="B36" t="n">
-        <v>90801</v>
+        <v>91739</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4520,25 +4517,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4548,10 +4545,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479274</v>
+        <v>479374</v>
       </c>
       <c r="R36" t="n">
-        <v>6951393</v>
+        <v>6951500</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4584,11 +4581,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4615,10 +4607,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154286</v>
+        <v>122154287</v>
       </c>
       <c r="B37" t="n">
-        <v>95744</v>
+        <v>78651</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4631,34 +4623,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479067</v>
+        <v>479072</v>
       </c>
       <c r="R37" t="n">
-        <v>6951710</v>
+        <v>6951714</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4717,10 +4713,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152404</v>
+        <v>122154282</v>
       </c>
       <c r="B38" t="n">
-        <v>90801</v>
+        <v>57532</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4733,34 +4729,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479269</v>
+        <v>478995</v>
       </c>
       <c r="R38" t="n">
-        <v>6951404</v>
+        <v>6951732</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4787,12 +4783,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,22 +4803,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152379</v>
+        <v>122152409</v>
       </c>
       <c r="B39" t="n">
-        <v>90801</v>
+        <v>90826</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4835,21 +4831,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4859,7 +4855,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479244</v>
+        <v>479277</v>
       </c>
       <c r="R39" t="n">
         <v>6951379</v>
@@ -4921,10 +4917,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154282</v>
+        <v>122152407</v>
       </c>
       <c r="B40" t="n">
-        <v>57532</v>
+        <v>90808</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4937,34 +4933,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478995</v>
+        <v>479274</v>
       </c>
       <c r="R40" t="n">
-        <v>6951732</v>
+        <v>6951393</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4991,12 +4987,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5011,22 +5012,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152377</v>
+        <v>122154285</v>
       </c>
       <c r="B41" t="n">
-        <v>91087</v>
+        <v>57490</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5035,38 +5036,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479251</v>
+        <v>479073</v>
       </c>
       <c r="R41" t="n">
-        <v>6951369</v>
+        <v>6951703</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5093,12 +5098,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5113,22 +5118,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152382</v>
+        <v>122152403</v>
       </c>
       <c r="B42" t="n">
-        <v>74743</v>
+        <v>91092</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5137,25 +5142,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>492</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5165,10 +5170,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479342</v>
+        <v>479265</v>
       </c>
       <c r="R42" t="n">
-        <v>6951436</v>
+        <v>6951415</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5227,10 +5232,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154328</v>
+        <v>122152382</v>
       </c>
       <c r="B43" t="n">
-        <v>79732</v>
+        <v>74743</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5239,25 +5244,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5267,10 +5272,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479349</v>
+        <v>479342</v>
       </c>
       <c r="R43" t="n">
-        <v>6951738</v>
+        <v>6951436</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5297,12 +5302,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5317,22 +5322,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122152383</v>
+        <v>122152379</v>
       </c>
       <c r="B44" t="n">
-        <v>91457</v>
+        <v>90808</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5341,38 +5346,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479355</v>
+        <v>479244</v>
       </c>
       <c r="R44" t="n">
-        <v>6951440</v>
+        <v>6951379</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5405,11 +5410,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5436,10 +5436,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122152392</v>
+        <v>122154283</v>
       </c>
       <c r="B45" t="n">
-        <v>91241</v>
+        <v>79767</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5448,38 +5448,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479310</v>
+        <v>479028</v>
       </c>
       <c r="R45" t="n">
-        <v>6951454</v>
+        <v>6951741</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5526,22 +5526,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122152395</v>
+        <v>122154338</v>
       </c>
       <c r="B46" t="n">
-        <v>91087</v>
+        <v>79732</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479310</v>
+        <v>479524</v>
       </c>
       <c r="R46" t="n">
-        <v>6951439</v>
+        <v>6951553</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5628,22 +5628,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122152409</v>
+        <v>122152392</v>
       </c>
       <c r="B47" t="n">
-        <v>90819</v>
+        <v>91246</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5652,38 +5652,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479277</v>
+        <v>479310</v>
       </c>
       <c r="R47" t="n">
-        <v>6951379</v>
+        <v>6951454</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,10 +5742,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122152400</v>
+        <v>122154331</v>
       </c>
       <c r="B48" t="n">
-        <v>74744</v>
+        <v>79732</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5758,21 +5758,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479288</v>
+        <v>479485</v>
       </c>
       <c r="R48" t="n">
-        <v>6951411</v>
+        <v>6951601</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,12 +5832,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -4917,10 +4917,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152407</v>
+        <v>122154285</v>
       </c>
       <c r="B40" t="n">
-        <v>90808</v>
+        <v>57490</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4929,38 +4929,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479274</v>
+        <v>479073</v>
       </c>
       <c r="R40" t="n">
-        <v>6951393</v>
+        <v>6951703</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4987,17 +4991,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5012,22 +5011,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154285</v>
+        <v>122152407</v>
       </c>
       <c r="B41" t="n">
-        <v>57490</v>
+        <v>90808</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5036,42 +5035,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479073</v>
+        <v>479274</v>
       </c>
       <c r="R41" t="n">
-        <v>6951703</v>
+        <v>6951393</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5098,12 +5093,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5118,12 +5118,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -4917,10 +4917,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154285</v>
+        <v>122152407</v>
       </c>
       <c r="B40" t="n">
-        <v>57490</v>
+        <v>90808</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4929,42 +4929,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479073</v>
+        <v>479274</v>
       </c>
       <c r="R40" t="n">
-        <v>6951703</v>
+        <v>6951393</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4991,12 +4987,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5011,22 +5012,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152407</v>
+        <v>122154285</v>
       </c>
       <c r="B41" t="n">
-        <v>90808</v>
+        <v>57490</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5035,38 +5036,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479274</v>
+        <v>479073</v>
       </c>
       <c r="R41" t="n">
-        <v>6951393</v>
+        <v>6951703</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5093,17 +5098,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5118,12 +5118,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152404</v>
+        <v>122154283</v>
       </c>
       <c r="B20" t="n">
-        <v>90808</v>
+        <v>79768</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,38 +2865,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6463</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479269</v>
+        <v>479028</v>
       </c>
       <c r="R20" t="n">
-        <v>6951404</v>
+        <v>6951741</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2923,12 +2918,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2943,12 +2938,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2958,7 +2953,7 @@
         <v>122152400</v>
       </c>
       <c r="B21" t="n">
-        <v>74744</v>
+        <v>74745</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2972,11 +2967,6 @@
       </c>
       <c r="E21" t="n">
         <v>308</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3060,7 +3050,7 @@
         <v>122152401</v>
       </c>
       <c r="B22" t="n">
-        <v>91092</v>
+        <v>91097</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3074,11 +3064,6 @@
       </c>
       <c r="E22" t="n">
         <v>658</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3159,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122152386</v>
+        <v>122154285</v>
       </c>
       <c r="B23" t="n">
-        <v>90826</v>
+        <v>57490</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3171,38 +3156,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>103031</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479347</v>
+        <v>479073</v>
       </c>
       <c r="R23" t="n">
-        <v>6951521</v>
+        <v>6951703</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3229,12 +3213,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3249,22 +3233,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152380</v>
+        <v>122152410</v>
       </c>
       <c r="B24" t="n">
-        <v>88123</v>
+        <v>97165</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3273,38 +3257,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479313</v>
+        <v>479306</v>
       </c>
       <c r="R24" t="n">
-        <v>6951347</v>
+        <v>6951356</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3345,6 +3328,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3363,10 +3347,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152377</v>
+        <v>122152409</v>
       </c>
       <c r="B25" t="n">
-        <v>91092</v>
+        <v>90831</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3379,21 +3363,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3403,10 +3382,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479251</v>
+        <v>479277</v>
       </c>
       <c r="R25" t="n">
-        <v>6951369</v>
+        <v>6951379</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3465,10 +3444,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154286</v>
+        <v>122152404</v>
       </c>
       <c r="B26" t="n">
-        <v>95749</v>
+        <v>90813</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,34 +3460,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479067</v>
+        <v>479269</v>
       </c>
       <c r="R26" t="n">
-        <v>6951710</v>
+        <v>6951404</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3535,12 +3509,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3555,22 +3529,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154328</v>
+        <v>122154284</v>
       </c>
       <c r="B27" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3585,11 +3559,6 @@
       <c r="E27" t="n">
         <v>6458</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -3603,14 +3572,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479349</v>
+        <v>479048</v>
       </c>
       <c r="R27" t="n">
-        <v>6951738</v>
+        <v>6951711</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,12 +3606,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,10 +3638,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152397</v>
+        <v>122152386</v>
       </c>
       <c r="B28" t="n">
-        <v>90826</v>
+        <v>90831</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3687,11 +3656,6 @@
       <c r="E28" t="n">
         <v>5432</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Porodaedalea chrysoloma</t>
@@ -3709,10 +3673,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479310</v>
+        <v>479347</v>
       </c>
       <c r="R28" t="n">
-        <v>6951433</v>
+        <v>6951521</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3771,10 +3735,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152383</v>
+        <v>122154286</v>
       </c>
       <c r="B29" t="n">
-        <v>91462</v>
+        <v>95758</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3783,38 +3747,33 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>898</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Blackticka</t>
-        </is>
+        <v>53</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479355</v>
+        <v>479067</v>
       </c>
       <c r="R29" t="n">
-        <v>6951440</v>
+        <v>6951710</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3841,17 +3800,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3866,22 +3820,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152388</v>
+        <v>122152382</v>
       </c>
       <c r="B30" t="n">
-        <v>91092</v>
+        <v>74744</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3890,25 +3844,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>492</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3918,10 +3867,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479294</v>
+        <v>479342</v>
       </c>
       <c r="R30" t="n">
-        <v>6951503</v>
+        <v>6951436</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3980,10 +3929,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152395</v>
+        <v>122152383</v>
       </c>
       <c r="B31" t="n">
-        <v>91092</v>
+        <v>91467</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3992,25 +3941,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>898</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4020,10 +3964,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479310</v>
+        <v>479355</v>
       </c>
       <c r="R31" t="n">
-        <v>6951439</v>
+        <v>6951440</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4056,6 +4000,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4082,10 +4031,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152376</v>
+        <v>122152379</v>
       </c>
       <c r="B32" t="n">
-        <v>97156</v>
+        <v>90813</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4094,42 +4043,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479264</v>
+        <v>479244</v>
       </c>
       <c r="R32" t="n">
-        <v>6951354</v>
+        <v>6951379</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4164,18 +4104,12 @@
           <t>2024-08-29</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogen.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4194,10 +4128,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154284</v>
+        <v>122152377</v>
       </c>
       <c r="B33" t="n">
-        <v>79732</v>
+        <v>91097</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4210,34 +4144,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>658</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479048</v>
+        <v>479251</v>
       </c>
       <c r="R33" t="n">
-        <v>6951711</v>
+        <v>6951369</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4264,12 +4193,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,22 +4213,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154280</v>
+        <v>122152376</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>97165</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4312,34 +4241,33 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479029</v>
+        <v>479264</v>
       </c>
       <c r="R34" t="n">
-        <v>6951739</v>
+        <v>6951354</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4366,12 +4294,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogen.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,28 +4313,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152410</v>
+        <v>122154287</v>
       </c>
       <c r="B35" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,42 +4344,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479306</v>
+        <v>479072</v>
       </c>
       <c r="R35" t="n">
-        <v>6951356</v>
+        <v>6951714</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4472,12 +4401,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4486,29 +4415,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152385</v>
+        <v>122152392</v>
       </c>
       <c r="B36" t="n">
-        <v>91739</v>
+        <v>91251</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4517,25 +4445,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Svavelriska</t>
-        </is>
+        <v>1209</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4545,10 +4468,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479374</v>
+        <v>479310</v>
       </c>
       <c r="R36" t="n">
-        <v>6951500</v>
+        <v>6951454</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4607,10 +4530,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154287</v>
+        <v>122154282</v>
       </c>
       <c r="B37" t="n">
-        <v>78651</v>
+        <v>57532</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4623,38 +4546,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479072</v>
+        <v>478995</v>
       </c>
       <c r="R37" t="n">
-        <v>6951714</v>
+        <v>6951732</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4713,10 +4627,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154282</v>
+        <v>122152403</v>
       </c>
       <c r="B38" t="n">
-        <v>57532</v>
+        <v>91097</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4729,34 +4643,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>658</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478995</v>
+        <v>479265</v>
       </c>
       <c r="R38" t="n">
-        <v>6951732</v>
+        <v>6951415</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4783,12 +4692,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4803,22 +4712,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152409</v>
+        <v>122154331</v>
       </c>
       <c r="B39" t="n">
-        <v>90826</v>
+        <v>79733</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4831,34 +4740,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479277</v>
+        <v>479485</v>
       </c>
       <c r="R39" t="n">
-        <v>6951379</v>
+        <v>6951601</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4885,12 +4789,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4905,22 +4809,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152407</v>
+        <v>122154280</v>
       </c>
       <c r="B40" t="n">
-        <v>90808</v>
+        <v>79637</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4929,38 +4833,33 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6456</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479274</v>
+        <v>479029</v>
       </c>
       <c r="R40" t="n">
-        <v>6951393</v>
+        <v>6951739</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4987,17 +4886,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5012,22 +4906,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154285</v>
+        <v>122154328</v>
       </c>
       <c r="B41" t="n">
-        <v>57490</v>
+        <v>79733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5036,42 +4930,33 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479073</v>
+        <v>479349</v>
       </c>
       <c r="R41" t="n">
-        <v>6951703</v>
+        <v>6951738</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5098,12 +4983,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5130,10 +5015,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152403</v>
+        <v>122152397</v>
       </c>
       <c r="B42" t="n">
-        <v>91092</v>
+        <v>90831</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5146,21 +5031,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5170,10 +5050,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479265</v>
+        <v>479310</v>
       </c>
       <c r="R42" t="n">
-        <v>6951415</v>
+        <v>6951433</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5232,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122152382</v>
+        <v>122152380</v>
       </c>
       <c r="B43" t="n">
-        <v>74743</v>
+        <v>88128</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5244,38 +5124,33 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>492</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Smalskaftslav</t>
-        </is>
+        <v>510</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479342</v>
+        <v>479313</v>
       </c>
       <c r="R43" t="n">
-        <v>6951436</v>
+        <v>6951347</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5334,10 +5209,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122152379</v>
+        <v>122152395</v>
       </c>
       <c r="B44" t="n">
-        <v>90808</v>
+        <v>91097</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5350,34 +5225,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>658</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479244</v>
+        <v>479310</v>
       </c>
       <c r="R44" t="n">
-        <v>6951379</v>
+        <v>6951439</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5436,10 +5306,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154283</v>
+        <v>122152407</v>
       </c>
       <c r="B45" t="n">
-        <v>79767</v>
+        <v>90813</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5448,38 +5318,33 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479028</v>
+        <v>479274</v>
       </c>
       <c r="R45" t="n">
-        <v>6951741</v>
+        <v>6951393</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5506,12 +5371,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5526,12 +5396,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5541,7 +5411,7 @@
         <v>122154338</v>
       </c>
       <c r="B46" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5555,11 +5425,6 @@
       </c>
       <c r="E46" t="n">
         <v>6458</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5640,10 +5505,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122152392</v>
+        <v>122152388</v>
       </c>
       <c r="B47" t="n">
-        <v>91246</v>
+        <v>91097</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5652,25 +5517,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>658</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5680,10 +5540,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479310</v>
+        <v>479294</v>
       </c>
       <c r="R47" t="n">
-        <v>6951454</v>
+        <v>6951503</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,10 +5602,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154331</v>
+        <v>122152385</v>
       </c>
       <c r="B48" t="n">
-        <v>79732</v>
+        <v>91744</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5754,25 +5614,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>4769</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5782,10 +5637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479485</v>
+        <v>479374</v>
       </c>
       <c r="R48" t="n">
-        <v>6951601</v>
+        <v>6951500</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5812,12 +5667,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,12 +5687,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -4332,10 +4332,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154287</v>
+        <v>122152392</v>
       </c>
       <c r="B35" t="n">
-        <v>78652</v>
+        <v>91251</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4344,37 +4344,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479072</v>
+        <v>479310</v>
       </c>
       <c r="R35" t="n">
-        <v>6951714</v>
+        <v>6951454</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4401,12 +4397,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4421,22 +4417,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122152392</v>
+        <v>122154287</v>
       </c>
       <c r="B36" t="n">
-        <v>91251</v>
+        <v>78652</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4445,33 +4441,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479310</v>
+        <v>479072</v>
       </c>
       <c r="R36" t="n">
-        <v>6951454</v>
+        <v>6951714</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4518,12 +4518,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2950,10 +2950,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152400</v>
+        <v>122152401</v>
       </c>
       <c r="B21" t="n">
-        <v>74745</v>
+        <v>91097</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479288</v>
+        <v>479280</v>
       </c>
       <c r="R21" t="n">
-        <v>6951411</v>
+        <v>6951418</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152401</v>
+        <v>122152400</v>
       </c>
       <c r="B22" t="n">
-        <v>91097</v>
+        <v>74745</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3063,16 +3063,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479280</v>
+        <v>479288</v>
       </c>
       <c r="R22" t="n">
-        <v>6951418</v>
+        <v>6951411</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154283</v>
+        <v>122152382</v>
       </c>
       <c r="B20" t="n">
-        <v>79768</v>
+        <v>74748</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,33 +2865,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>492</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479028</v>
+        <v>479342</v>
       </c>
       <c r="R20" t="n">
-        <v>6951741</v>
+        <v>6951436</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2918,12 +2923,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,22 +2943,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122152401</v>
+        <v>122152383</v>
       </c>
       <c r="B21" t="n">
-        <v>91097</v>
+        <v>91480</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2962,20 +2967,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>898</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2985,10 +2995,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479280</v>
+        <v>479355</v>
       </c>
       <c r="R21" t="n">
-        <v>6951418</v>
+        <v>6951440</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3021,6 +3031,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3047,10 +3062,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152400</v>
+        <v>122152407</v>
       </c>
       <c r="B22" t="n">
-        <v>74745</v>
+        <v>90826</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3063,16 +3078,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3082,10 +3102,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479288</v>
+        <v>479274</v>
       </c>
       <c r="R22" t="n">
-        <v>6951411</v>
+        <v>6951393</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3118,6 +3138,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3144,10 +3169,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154285</v>
+        <v>122154280</v>
       </c>
       <c r="B23" t="n">
-        <v>57490</v>
+        <v>79641</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,33 +3185,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>6456</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479073</v>
+        <v>479029</v>
       </c>
       <c r="R23" t="n">
-        <v>6951703</v>
+        <v>6951739</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3245,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122152410</v>
+        <v>122154285</v>
       </c>
       <c r="B24" t="n">
-        <v>97165</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3261,33 +3287,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>103031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479306</v>
+        <v>479073</v>
       </c>
       <c r="R24" t="n">
-        <v>6951356</v>
+        <v>6951703</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3314,12 +3345,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,29 +3359,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152409</v>
+        <v>122152376</v>
       </c>
       <c r="B25" t="n">
-        <v>90831</v>
+        <v>97178</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3359,33 +3389,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479277</v>
+        <v>479264</v>
       </c>
       <c r="R25" t="n">
-        <v>6951379</v>
+        <v>6951354</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3420,12 +3459,18 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogen.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3444,10 +3489,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152404</v>
+        <v>122152397</v>
       </c>
       <c r="B26" t="n">
-        <v>90813</v>
+        <v>90844</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,16 +3505,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3479,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479269</v>
+        <v>479310</v>
       </c>
       <c r="R26" t="n">
-        <v>6951404</v>
+        <v>6951433</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3541,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154284</v>
+        <v>122152377</v>
       </c>
       <c r="B27" t="n">
-        <v>79733</v>
+        <v>91110</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3557,29 +3607,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>658</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479048</v>
+        <v>479251</v>
       </c>
       <c r="R27" t="n">
-        <v>6951711</v>
+        <v>6951369</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3606,12 +3661,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,22 +3681,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152386</v>
+        <v>122152403</v>
       </c>
       <c r="B28" t="n">
-        <v>90831</v>
+        <v>91110</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3654,16 +3709,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>658</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3673,10 +3733,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479347</v>
+        <v>479265</v>
       </c>
       <c r="R28" t="n">
-        <v>6951521</v>
+        <v>6951415</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3735,10 +3795,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154286</v>
+        <v>122154287</v>
       </c>
       <c r="B29" t="n">
-        <v>95758</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3751,29 +3811,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479067</v>
+        <v>479072</v>
       </c>
       <c r="R29" t="n">
-        <v>6951710</v>
+        <v>6951714</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3832,10 +3901,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152382</v>
+        <v>122152392</v>
       </c>
       <c r="B30" t="n">
-        <v>74744</v>
+        <v>91264</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3848,16 +3917,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>492</v>
+        <v>1209</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3867,10 +3941,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479342</v>
+        <v>479310</v>
       </c>
       <c r="R30" t="n">
-        <v>6951436</v>
+        <v>6951454</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3929,10 +4003,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122152383</v>
+        <v>122154331</v>
       </c>
       <c r="B31" t="n">
-        <v>91467</v>
+        <v>79737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3941,20 +4015,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3964,10 +4043,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479355</v>
+        <v>479485</v>
       </c>
       <c r="R31" t="n">
-        <v>6951440</v>
+        <v>6951601</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,17 +4073,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På murken granlåga. Delvis ovanpå gammal fruktkropp av ullticka.</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4019,22 +4093,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122152379</v>
+        <v>122154328</v>
       </c>
       <c r="B32" t="n">
-        <v>90813</v>
+        <v>79737</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4047,29 +4121,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479244</v>
+        <v>479349</v>
       </c>
       <c r="R32" t="n">
-        <v>6951379</v>
+        <v>6951738</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4096,12 +4175,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4116,22 +4195,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152377</v>
+        <v>122152386</v>
       </c>
       <c r="B33" t="n">
-        <v>91097</v>
+        <v>90844</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4144,29 +4223,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>5432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479251</v>
+        <v>479347</v>
       </c>
       <c r="R33" t="n">
-        <v>6951369</v>
+        <v>6951521</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4225,10 +4309,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152376</v>
+        <v>122152388</v>
       </c>
       <c r="B34" t="n">
-        <v>97165</v>
+        <v>91110</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4237,37 +4321,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>658</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479264</v>
+        <v>479294</v>
       </c>
       <c r="R34" t="n">
-        <v>6951354</v>
+        <v>6951503</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4302,18 +4387,12 @@
           <t>2024-08-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogen.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4332,10 +4411,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152392</v>
+        <v>122152404</v>
       </c>
       <c r="B35" t="n">
-        <v>91251</v>
+        <v>90826</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4344,20 +4423,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4367,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479310</v>
+        <v>479269</v>
       </c>
       <c r="R35" t="n">
-        <v>6951454</v>
+        <v>6951404</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4429,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154287</v>
+        <v>122154286</v>
       </c>
       <c r="B36" t="n">
-        <v>78652</v>
+        <v>95771</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4445,33 +4529,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>53</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479072</v>
+        <v>479067</v>
       </c>
       <c r="R36" t="n">
-        <v>6951714</v>
+        <v>6951710</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4530,10 +4615,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154282</v>
+        <v>122154283</v>
       </c>
       <c r="B37" t="n">
-        <v>57532</v>
+        <v>79772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4542,20 +4627,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6463</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4565,10 +4655,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478995</v>
+        <v>479028</v>
       </c>
       <c r="R37" t="n">
-        <v>6951732</v>
+        <v>6951741</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4627,10 +4717,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152403</v>
+        <v>122152401</v>
       </c>
       <c r="B38" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4645,6 +4735,11 @@
       <c r="E38" t="n">
         <v>658</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Rhodofomes roseus</t>
@@ -4662,10 +4757,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479265</v>
+        <v>479280</v>
       </c>
       <c r="R38" t="n">
-        <v>6951415</v>
+        <v>6951418</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4724,10 +4819,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154331</v>
+        <v>122152395</v>
       </c>
       <c r="B39" t="n">
-        <v>79733</v>
+        <v>91110</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4740,16 +4835,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4759,10 +4859,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479485</v>
+        <v>479310</v>
       </c>
       <c r="R39" t="n">
-        <v>6951601</v>
+        <v>6951439</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4789,12 +4889,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4809,22 +4909,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154280</v>
+        <v>122152379</v>
       </c>
       <c r="B40" t="n">
-        <v>79637</v>
+        <v>90826</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4833,33 +4933,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479029</v>
+        <v>479244</v>
       </c>
       <c r="R40" t="n">
-        <v>6951739</v>
+        <v>6951379</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4886,12 +4991,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4906,22 +5011,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154328</v>
+        <v>122152385</v>
       </c>
       <c r="B41" t="n">
-        <v>79733</v>
+        <v>91757</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4930,20 +5035,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>4769</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4953,10 +5063,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479349</v>
+        <v>479374</v>
       </c>
       <c r="R41" t="n">
-        <v>6951738</v>
+        <v>6951500</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4983,12 +5093,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,22 +5113,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122152397</v>
+        <v>122154284</v>
       </c>
       <c r="B42" t="n">
-        <v>90831</v>
+        <v>79737</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5031,29 +5141,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479310</v>
+        <v>479048</v>
       </c>
       <c r="R42" t="n">
-        <v>6951433</v>
+        <v>6951711</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5080,12 +5195,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5100,22 +5215,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122152380</v>
+        <v>122152409</v>
       </c>
       <c r="B43" t="n">
-        <v>88128</v>
+        <v>90844</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5128,16 +5243,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>5432</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5147,10 +5267,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479313</v>
+        <v>479277</v>
       </c>
       <c r="R43" t="n">
-        <v>6951347</v>
+        <v>6951379</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5209,10 +5329,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122152395</v>
+        <v>122152400</v>
       </c>
       <c r="B44" t="n">
-        <v>91097</v>
+        <v>74749</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5225,16 +5345,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>308</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5244,10 +5369,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479310</v>
+        <v>479288</v>
       </c>
       <c r="R44" t="n">
-        <v>6951439</v>
+        <v>6951411</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5306,10 +5431,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122152407</v>
+        <v>122154282</v>
       </c>
       <c r="B45" t="n">
-        <v>90813</v>
+        <v>57536</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5322,29 +5447,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479274</v>
+        <v>478995</v>
       </c>
       <c r="R45" t="n">
-        <v>6951393</v>
+        <v>6951732</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5371,17 +5501,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5396,12 +5521,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5411,7 +5536,7 @@
         <v>122154338</v>
       </c>
       <c r="B46" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5425,6 +5550,11 @@
       </c>
       <c r="E46" t="n">
         <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5505,10 +5635,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122152388</v>
+        <v>122152380</v>
       </c>
       <c r="B47" t="n">
-        <v>91097</v>
+        <v>88141</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5521,29 +5651,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>510</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479294</v>
+        <v>479313</v>
       </c>
       <c r="R47" t="n">
-        <v>6951503</v>
+        <v>6951347</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5602,10 +5737,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122152385</v>
+        <v>122152410</v>
       </c>
       <c r="B48" t="n">
-        <v>91744</v>
+        <v>97178</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5618,29 +5753,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479374</v>
+        <v>479306</v>
       </c>
       <c r="R48" t="n">
-        <v>6951500</v>
+        <v>6951356</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5681,6 +5825,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122152382</v>
+        <v>122152409</v>
       </c>
       <c r="B20" t="n">
-        <v>74748</v>
+        <v>90857</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,38 +2865,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479342</v>
+        <v>479277</v>
       </c>
       <c r="R20" t="n">
-        <v>6951436</v>
+        <v>6951379</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2958,7 +2958,7 @@
         <v>122152383</v>
       </c>
       <c r="B21" t="n">
-        <v>91480</v>
+        <v>91493</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122152407</v>
+        <v>122154287</v>
       </c>
       <c r="B22" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3078,34 +3078,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479274</v>
+        <v>479072</v>
       </c>
       <c r="R22" t="n">
-        <v>6951393</v>
+        <v>6951714</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3132,17 +3136,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3157,22 +3156,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154280</v>
+        <v>122152401</v>
       </c>
       <c r="B23" t="n">
-        <v>79641</v>
+        <v>91123</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3181,38 +3180,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479029</v>
+        <v>479280</v>
       </c>
       <c r="R23" t="n">
-        <v>6951739</v>
+        <v>6951418</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3239,12 +3238,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3259,22 +3258,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154285</v>
+        <v>122154338</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>79737</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3283,42 +3282,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479073</v>
+        <v>479524</v>
       </c>
       <c r="R24" t="n">
-        <v>6951703</v>
+        <v>6951553</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3345,12 +3340,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3377,10 +3372,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122152376</v>
+        <v>122152382</v>
       </c>
       <c r="B25" t="n">
-        <v>97178</v>
+        <v>74748</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3389,42 +3384,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>492</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479264</v>
+        <v>479342</v>
       </c>
       <c r="R25" t="n">
-        <v>6951354</v>
+        <v>6951436</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3459,18 +3450,12 @@
           <t>2024-08-29</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogen.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3489,10 +3474,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122152397</v>
+        <v>122154286</v>
       </c>
       <c r="B26" t="n">
-        <v>90844</v>
+        <v>95784</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3505,34 +3490,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479310</v>
+        <v>479067</v>
       </c>
       <c r="R26" t="n">
-        <v>6951433</v>
+        <v>6951710</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3559,12 +3544,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3579,22 +3564,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122152377</v>
+        <v>122152388</v>
       </c>
       <c r="B27" t="n">
-        <v>91110</v>
+        <v>91123</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3627,14 +3612,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479251</v>
+        <v>479294</v>
       </c>
       <c r="R27" t="n">
-        <v>6951369</v>
+        <v>6951503</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3693,10 +3678,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122152403</v>
+        <v>122154280</v>
       </c>
       <c r="B28" t="n">
-        <v>91110</v>
+        <v>79641</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3705,38 +3690,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479265</v>
+        <v>479029</v>
       </c>
       <c r="R28" t="n">
-        <v>6951415</v>
+        <v>6951739</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3763,12 +3748,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,22 +3768,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154287</v>
+        <v>122152410</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3807,42 +3792,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479072</v>
+        <v>479306</v>
       </c>
       <c r="R29" t="n">
-        <v>6951714</v>
+        <v>6951356</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3869,12 +3854,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3883,28 +3868,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152392</v>
+        <v>122152407</v>
       </c>
       <c r="B30" t="n">
-        <v>91264</v>
+        <v>90839</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,25 +3899,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3941,10 +3927,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479310</v>
+        <v>479274</v>
       </c>
       <c r="R30" t="n">
-        <v>6951454</v>
+        <v>6951393</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3977,6 +3963,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4003,10 +3994,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154331</v>
+        <v>122154283</v>
       </c>
       <c r="B31" t="n">
-        <v>79737</v>
+        <v>79772</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4015,38 +4006,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479485</v>
+        <v>479028</v>
       </c>
       <c r="R31" t="n">
-        <v>6951601</v>
+        <v>6951741</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4073,12 +4064,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4105,10 +4096,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154328</v>
+        <v>122152397</v>
       </c>
       <c r="B32" t="n">
-        <v>79737</v>
+        <v>90857</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4121,21 +4112,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4145,10 +4136,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479349</v>
+        <v>479310</v>
       </c>
       <c r="R32" t="n">
-        <v>6951738</v>
+        <v>6951433</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4175,12 +4166,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4195,22 +4186,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122152386</v>
+        <v>122154285</v>
       </c>
       <c r="B33" t="n">
-        <v>90844</v>
+        <v>57494</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4219,38 +4210,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479347</v>
+        <v>479073</v>
       </c>
       <c r="R33" t="n">
-        <v>6951521</v>
+        <v>6951703</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4277,12 +4272,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,22 +4292,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122152388</v>
+        <v>122152392</v>
       </c>
       <c r="B34" t="n">
-        <v>91110</v>
+        <v>91277</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4321,25 +4316,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4349,10 +4344,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479294</v>
+        <v>479310</v>
       </c>
       <c r="R34" t="n">
-        <v>6951503</v>
+        <v>6951454</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4411,10 +4406,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122152404</v>
+        <v>122152379</v>
       </c>
       <c r="B35" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4447,14 +4442,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479269</v>
+        <v>479244</v>
       </c>
       <c r="R35" t="n">
-        <v>6951404</v>
+        <v>6951379</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4513,10 +4508,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154286</v>
+        <v>122152400</v>
       </c>
       <c r="B36" t="n">
-        <v>95771</v>
+        <v>74749</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4529,34 +4524,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479067</v>
+        <v>479288</v>
       </c>
       <c r="R36" t="n">
-        <v>6951710</v>
+        <v>6951411</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4583,12 +4578,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4603,22 +4598,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154283</v>
+        <v>122152386</v>
       </c>
       <c r="B37" t="n">
-        <v>79772</v>
+        <v>90857</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4627,38 +4622,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479028</v>
+        <v>479347</v>
       </c>
       <c r="R37" t="n">
-        <v>6951741</v>
+        <v>6951521</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4685,12 +4680,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4705,22 +4700,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122152401</v>
+        <v>122152385</v>
       </c>
       <c r="B38" t="n">
-        <v>91110</v>
+        <v>91770</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4729,25 +4724,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4757,10 +4752,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479280</v>
+        <v>479374</v>
       </c>
       <c r="R38" t="n">
-        <v>6951418</v>
+        <v>6951500</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4819,10 +4814,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122152395</v>
+        <v>122152377</v>
       </c>
       <c r="B39" t="n">
-        <v>91110</v>
+        <v>91123</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4855,14 +4850,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479310</v>
+        <v>479251</v>
       </c>
       <c r="R39" t="n">
-        <v>6951439</v>
+        <v>6951369</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4921,10 +4916,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122152379</v>
+        <v>122152395</v>
       </c>
       <c r="B40" t="n">
-        <v>90826</v>
+        <v>91123</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4937,34 +4932,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479244</v>
+        <v>479310</v>
       </c>
       <c r="R40" t="n">
-        <v>6951379</v>
+        <v>6951439</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5023,10 +5018,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122152385</v>
+        <v>122154331</v>
       </c>
       <c r="B41" t="n">
-        <v>91757</v>
+        <v>79737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5035,25 +5030,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5063,10 +5058,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479374</v>
+        <v>479485</v>
       </c>
       <c r="R41" t="n">
-        <v>6951500</v>
+        <v>6951601</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5093,12 +5088,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5113,19 +5108,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154284</v>
+        <v>122154328</v>
       </c>
       <c r="B42" t="n">
         <v>79737</v>
@@ -5161,14 +5156,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479048</v>
+        <v>479349</v>
       </c>
       <c r="R42" t="n">
-        <v>6951711</v>
+        <v>6951738</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5195,12 +5190,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,10 +5222,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122152409</v>
+        <v>122152380</v>
       </c>
       <c r="B43" t="n">
-        <v>90844</v>
+        <v>88192</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5243,21 +5238,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5267,10 +5262,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479277</v>
+        <v>479313</v>
       </c>
       <c r="R43" t="n">
-        <v>6951379</v>
+        <v>6951347</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5329,10 +5324,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122152400</v>
+        <v>122152403</v>
       </c>
       <c r="B44" t="n">
-        <v>74749</v>
+        <v>91123</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5345,21 +5340,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5369,10 +5364,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479288</v>
+        <v>479265</v>
       </c>
       <c r="R44" t="n">
-        <v>6951411</v>
+        <v>6951415</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5431,10 +5426,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154282</v>
+        <v>122152404</v>
       </c>
       <c r="B45" t="n">
-        <v>57536</v>
+        <v>90839</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5447,34 +5442,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478995</v>
+        <v>479269</v>
       </c>
       <c r="R45" t="n">
-        <v>6951732</v>
+        <v>6951404</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5501,12 +5496,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5521,22 +5516,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154338</v>
+        <v>122154282</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5549,34 +5544,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479524</v>
+        <v>478995</v>
       </c>
       <c r="R46" t="n">
-        <v>6951553</v>
+        <v>6951732</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5603,12 +5598,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5635,10 +5630,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122152380</v>
+        <v>122154284</v>
       </c>
       <c r="B47" t="n">
-        <v>88141</v>
+        <v>79737</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5651,34 +5646,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479313</v>
+        <v>479048</v>
       </c>
       <c r="R47" t="n">
-        <v>6951347</v>
+        <v>6951711</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5705,12 +5700,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5725,22 +5720,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122152410</v>
+        <v>122152376</v>
       </c>
       <c r="B48" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5781,10 +5776,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479306</v>
+        <v>479264</v>
       </c>
       <c r="R48" t="n">
-        <v>6951356</v>
+        <v>6951354</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5817,6 +5812,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogen.</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 2145-2022 artfynd.xlsx
+++ b/artfynd/A 2145-2022 artfynd.xlsx
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122152410</v>
+        <v>122152407</v>
       </c>
       <c r="B29" t="n">
-        <v>97191</v>
+        <v>90839</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3792,42 +3792,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479306</v>
+        <v>479274</v>
       </c>
       <c r="R29" t="n">
-        <v>6951356</v>
+        <v>6951393</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3862,13 +3858,17 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122152407</v>
+        <v>122152410</v>
       </c>
       <c r="B30" t="n">
-        <v>90839</v>
+        <v>97191</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3899,38 +3899,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479274</v>
+        <v>479306</v>
       </c>
       <c r="R30" t="n">
-        <v>6951393</v>
+        <v>6951356</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3965,17 +3969,13 @@
           <t>2024-08-29</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På upplyft, murken, mossig granlåga i fuktig granskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -5528,10 +5528,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154282</v>
+        <v>122152376</v>
       </c>
       <c r="B46" t="n">
-        <v>57536</v>
+        <v>97191</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5540,38 +5540,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478995</v>
+        <v>479264</v>
       </c>
       <c r="R46" t="n">
-        <v>6951732</v>
+        <v>6951354</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5598,12 +5602,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5612,18 +5621,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5732,10 +5742,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122152376</v>
+        <v>122154282</v>
       </c>
       <c r="B48" t="n">
-        <v>97191</v>
+        <v>57536</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5744,42 +5754,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479264</v>
+        <v>478995</v>
       </c>
       <c r="R48" t="n">
-        <v>6951354</v>
+        <v>6951732</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5806,17 +5812,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogen.</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5825,19 +5826,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
